--- a/ksoft_old/docs/fields_details/jalmeida/CE0302(1).xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302(1).xlsx
@@ -7211,13 +7211,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12A98C72-3095-4837-95CE-3546E510C163}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EC10272-7D63-4253-BB48-2D88C290B9B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B808B5A9-44FE-4C78-89FC-DE51C9C4BE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB6CDC2C-3454-4B5F-98B4-04D0DB33071B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96E5FFD2-6BB4-4B58-9331-B33A4641CB6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0EF0D1-4AF6-4FEF-A6A6-3596CEF4B87B}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CE0302(1).xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302(1).xlsx
@@ -7211,13 +7211,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EC10272-7D63-4253-BB48-2D88C290B9B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5DD437D-0BE1-4C02-B201-14E5ACEA35E9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB6CDC2C-3454-4B5F-98B4-04D0DB33071B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D67E850-6236-4760-A3AD-6803CF9CE28F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0EF0D1-4AF6-4FEF-A6A6-3596CEF4B87B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB44A0B-6796-4228-BF6C-C1AC7D677DF8}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CE0302(1).xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302(1).xlsx
@@ -7211,13 +7211,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5DD437D-0BE1-4C02-B201-14E5ACEA35E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12A98C72-3095-4837-95CE-3546E510C163}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D67E850-6236-4760-A3AD-6803CF9CE28F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B808B5A9-44FE-4C78-89FC-DE51C9C4BE0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB44A0B-6796-4228-BF6C-C1AC7D677DF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96E5FFD2-6BB4-4B58-9331-B33A4641CB6E}"/>
 </file>